--- a/data/trans_dic/P16A_2_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A_2_R3-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 18,37</t>
+          <t>7,16; 19,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,24; 25,18</t>
+          <t>13,81; 25,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,88; 19,62</t>
+          <t>11,36; 19,58</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,71; 24,69</t>
+          <t>14,17; 24,49</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,97; 24,18</t>
+          <t>11,74; 24,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,35; 22,27</t>
+          <t>14,43; 22,65</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,86; 21,89</t>
+          <t>14,66; 21,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,45; 31,76</t>
+          <t>20,29; 31,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,83; 25,91</t>
+          <t>19,44; 25,84</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,0; 26,06</t>
+          <t>7,86; 26,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,91; 40,15</t>
+          <t>30,31; 39,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,13; 32,03</t>
+          <t>16,34; 32,01</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,84; 33,16</t>
+          <t>25,89; 33,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40,49; 46,76</t>
+          <t>40,15; 46,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,13; 38,89</t>
+          <t>33,82; 38,98</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,34; 30,64</t>
+          <t>23,78; 31,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51,59; 86,22</t>
+          <t>51,2; 85,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39,51; 74,36</t>
+          <t>39,77; 74,86</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>35,17; 44,56</t>
+          <t>35,88; 44,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63,62; 70,18</t>
+          <t>63,44; 70,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53,48; 59,11</t>
+          <t>53,56; 58,91</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,17; 24,48</t>
+          <t>17,33; 24,65</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36,85; 52,44</t>
+          <t>36,94; 52,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28,71; 38,45</t>
+          <t>28,84; 37,7</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas</t>
+          <t>Población que ha consumido medicinas para el dolor en las dos últimas semanas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>26784; 73481</t>
+          <t>28627; 76824</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41467; 78868</t>
+          <t>43260; 79990</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77630; 139927</t>
+          <t>81023; 139661</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>62287; 104568</t>
+          <t>60002; 103746</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61285; 123823</t>
+          <t>60132; 123184</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>134268; 208336</t>
+          <t>135015; 211945</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>79692; 117410</t>
+          <t>78625; 116240</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>126958; 188031</t>
+          <t>120147; 186383</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>223798; 292360</t>
+          <t>219356; 291599</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71027; 231357</t>
+          <t>69753; 233296</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>220357; 286243</t>
+          <t>216074; 283234</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>258135; 512721</t>
+          <t>261587; 512337</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>145045; 186127</t>
+          <t>145308; 185903</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>221827; 256189</t>
+          <t>219963; 255225</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>378556; 431309</t>
+          <t>375156; 432294</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>85921; 112819</t>
+          <t>87561; 115651</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>313832; 524515</t>
+          <t>311507; 518616</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>385787; 726114</t>
+          <t>388361; 731033</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>99438; 125997</t>
+          <t>101458; 127022</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>270911; 298861</t>
+          <t>270166; 298170</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>378946; 418879</t>
+          <t>379507; 417443</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>594040; 847131</t>
+          <t>599658; 852926</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1367959; 1946538</t>
+          <t>1371287; 1936484</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2059043; 2757995</t>
+          <t>2068179; 2703878</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A_2_R3-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P16A_2_R3-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,16; 19,21</t>
+          <t>7,19; 17,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,81; 25,54</t>
+          <t>14,5; 26,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,36; 19,58</t>
+          <t>12,13; 20,15</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,17; 24,49</t>
+          <t>13,84; 23,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,74; 24,06</t>
+          <t>16,89; 24,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,43; 22,65</t>
+          <t>16,68; 22,78</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,6%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,66; 21,67</t>
+          <t>14,13; 20,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,29; 31,48</t>
+          <t>26,59; 33,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19,44; 25,84</t>
+          <t>21,46; 25,91</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>31,09%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 26,28</t>
+          <t>21,22; 28,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,31; 39,73</t>
+          <t>34,59; 40,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,34; 32,01</t>
+          <t>29,0; 33,52</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,89; 33,12</t>
+          <t>25,98; 32,94</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40,15; 46,58</t>
+          <t>40,54; 46,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,82; 38,98</t>
+          <t>34,02; 38,92</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>52,51%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>40,15%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,78; 31,41</t>
+          <t>23,49; 30,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51,2; 85,25</t>
+          <t>49,17; 55,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>39,77; 74,86</t>
+          <t>37,69; 42,99</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>55,79%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>35,88; 44,92</t>
+          <t>34,97; 44,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63,44; 70,02</t>
+          <t>62,88; 69,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53,56; 58,91</t>
+          <t>52,94; 58,46</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,19%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>17,33; 24,65</t>
+          <t>21,95; 25,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>36,94; 52,16</t>
+          <t>37,21; 39,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28,84; 37,7</t>
+          <t>30,12; 32,29</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>46435</t>
+          <t>47676</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59490</t>
+          <t>71354</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105925</t>
+          <t>119030</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28627; 76824</t>
+          <t>29319; 70972</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>43260; 79990</t>
+          <t>52562; 95606</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>81023; 139661</t>
+          <t>93472; 155233</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>80559</t>
+          <t>88636</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>97484</t>
+          <t>103976</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>178043</t>
+          <t>192612</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60002; 103746</t>
+          <t>66012; 113786</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60132; 123184</t>
+          <t>84760; 122860</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>135015; 211945</t>
+          <t>163278; 222962</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>108173</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>163912</t>
+          <t>185384</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>261647</t>
+          <t>293556</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>78625; 116240</t>
+          <t>87748; 129983</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>120147; 186383</t>
+          <t>165730; 205943</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>219356; 291599</t>
+          <t>266987; 322299</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>160751</t>
+          <t>172356</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>260063</t>
+          <t>274540</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>420814</t>
+          <t>446896</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>69753; 233296</t>
+          <t>148694; 196560</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>216074; 283234</t>
+          <t>254913; 295347</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>261587; 512337</t>
+          <t>416934; 481877</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>167352</t>
+          <t>178850</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>238581</t>
+          <t>264703</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>405932</t>
+          <t>443554</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>145308; 185903</t>
+          <t>158293; 200725</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>219963; 255225</t>
+          <t>246836; 284036</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>375156; 432294</t>
+          <t>414432; 474159</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>100556</t>
+          <t>109141</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>417128</t>
+          <t>230620</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>517683</t>
+          <t>339761</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>87561; 115651</t>
+          <t>95612; 124696</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>311507; 518616</t>
+          <t>215956; 245189</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>388361; 731033</t>
+          <t>318963; 363801</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>113511</t>
+          <t>123203</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>285297</t>
+          <t>309062</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>398808</t>
+          <t>432266</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>101458; 127022</t>
+          <t>108490; 137537</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>270166; 298170</t>
+          <t>292125; 322458</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>379507; 417443</t>
+          <t>410221; 452965</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>766900</t>
+          <t>828035</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1521954</t>
+          <t>1439640</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2288854</t>
+          <t>2267675</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>599658; 852926</t>
+          <t>775545; 887853</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1371287; 1936484</t>
+          <t>1390477; 1492474</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2068179; 2703878</t>
+          <t>2189604; 2347341</t>
         </is>
       </c>
     </row>
